--- a/Team-Data/2011-12/4-1-2011-12.xlsx
+++ b/Team-Data/2011-12/4-1-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -748,19 +815,19 @@
         <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ2" t="n">
         <v>16</v>
       </c>
       <c r="AK2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -781,25 +848,25 @@
         <v>24</v>
       </c>
       <c r="AR2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -814,7 +881,7 @@
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -843,55 +910,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
         <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>0.577</v>
+        <v>0.569</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L3" t="n">
         <v>5.4</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O3" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P3" t="n">
         <v>20.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.781</v>
+        <v>0.778</v>
       </c>
       <c r="R3" t="n">
         <v>7.9</v>
       </c>
       <c r="S3" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="T3" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="U3" t="n">
         <v>23.6</v>
@@ -906,34 +973,34 @@
         <v>5.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
         <v>20.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB3" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF3" t="n">
         <v>9</v>
       </c>
       <c r="AG3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>22</v>
@@ -945,22 +1012,22 @@
         <v>5</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN3" t="n">
         <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
@@ -975,16 +1042,16 @@
         <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
         <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -996,7 +1063,7 @@
         <v>27</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-12.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1142,10 +1209,10 @@
         <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1163,16 +1230,16 @@
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ4" t="n">
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -1207,85 +1274,85 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
         <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>0.778</v>
+        <v>0.792</v>
       </c>
       <c r="H5" t="n">
         <v>48.1</v>
       </c>
       <c r="I5" t="n">
-        <v>37.5</v>
+        <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
         <v>6.3</v>
       </c>
       <c r="M5" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="R5" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="S5" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V5" t="n">
         <v>13.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1300,16 +1367,16 @@
         <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AL5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM5" t="n">
         <v>19</v>
@@ -1318,13 +1385,13 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>25</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>26</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1348,7 +1415,7 @@
         <v>3</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>1</v>
@@ -1357,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>-5.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF6" t="n">
         <v>23</v>
@@ -1479,7 +1546,7 @@
         <v>26</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>28</v>
@@ -1503,7 +1570,7 @@
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
@@ -1661,13 +1728,13 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>14</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>13</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
@@ -1682,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>25</v>
@@ -1709,7 +1776,7 @@
         <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
         <v>2</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
         <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.547</v>
+        <v>0.538</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
@@ -1771,10 +1838,10 @@
         <v>38.3</v>
       </c>
       <c r="J8" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
         <v>6.5</v>
@@ -1783,37 +1850,37 @@
         <v>20.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.323</v>
+        <v>0.321</v>
       </c>
       <c r="O8" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="P8" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0.738</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S8" t="n">
         <v>32.5</v>
       </c>
       <c r="T8" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
         <v>15.9</v>
       </c>
       <c r="W8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y8" t="n">
         <v>6.4</v>
@@ -1822,19 +1889,19 @@
         <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB8" t="n">
         <v>103.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
@@ -1855,7 +1922,7 @@
         <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM8" t="n">
         <v>10</v>
@@ -1873,7 +1940,7 @@
         <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>4</v>
@@ -1888,7 +1955,7 @@
         <v>28</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
         <v>13</v>
@@ -1897,16 +1964,16 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="n">
         <v>2</v>
       </c>
-      <c r="BB8" t="n">
-        <v>1</v>
-      </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
         <v>26</v>
@@ -2049,7 +2116,7 @@
         <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>0.392</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J10" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L10" t="n">
         <v>8.1</v>
@@ -2147,31 +2214,31 @@
         <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.387</v>
+        <v>0.384</v>
       </c>
       <c r="O10" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P10" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R10" t="n">
         <v>9.6</v>
       </c>
       <c r="S10" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="T10" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="U10" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="V10" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W10" t="n">
         <v>8</v>
@@ -2180,7 +2247,7 @@
         <v>5.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z10" t="n">
         <v>21.7</v>
@@ -2189,10 +2256,10 @@
         <v>17.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AD10" t="n">
         <v>25</v>
@@ -2207,19 +2274,19 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
         <v>8</v>
@@ -2228,19 +2295,19 @@
         <v>2</v>
       </c>
       <c r="AO10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP10" t="n">
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
       </c>
       <c r="AS10" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
         <v>28</v>
@@ -2249,7 +2316,7 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
         <v>12</v>
@@ -2258,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -2299,61 +2366,61 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
         <v>28</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.528</v>
+        <v>0.538</v>
       </c>
       <c r="H11" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J11" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="K11" t="n">
         <v>0.453</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M11" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O11" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S11" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T11" t="n">
         <v>42.2</v>
       </c>
       <c r="U11" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V11" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W11" t="n">
         <v>7.3</v>
@@ -2362,13 +2429,13 @@
         <v>4.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z11" t="n">
         <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB11" t="n">
         <v>98.09999999999999</v>
@@ -2377,25 +2444,25 @@
         <v>0.6</v>
       </c>
       <c r="AD11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH11" t="n">
         <v>5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3</v>
-      </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>11</v>
@@ -2410,13 +2477,13 @@
         <v>11</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>15</v>
@@ -2428,22 +2495,22 @@
         <v>16</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW11" t="n">
         <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>20</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>22</v>
       </c>
       <c r="BA11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -2481,19 +2548,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.596</v>
+        <v>0.588</v>
       </c>
       <c r="H12" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I12" t="n">
         <v>35.2</v>
@@ -2505,73 +2572,73 @@
         <v>0.437</v>
       </c>
       <c r="L12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M12" t="n">
         <v>15.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="O12" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P12" t="n">
         <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="V12" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W12" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
         <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>96.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AC12" t="n">
         <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF12" t="n">
         <v>7</v>
       </c>
-      <c r="AF12" t="n">
-        <v>6</v>
-      </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>23</v>
@@ -2580,7 +2647,7 @@
         <v>21</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>19</v>
@@ -2598,13 +2665,13 @@
         <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -2619,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
       </c>
       <c r="AF13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG13" t="n">
         <v>7</v>
@@ -2786,7 +2853,7 @@
         <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT13" t="n">
         <v>20</v>
@@ -2798,10 +2865,10 @@
         <v>3</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY13" t="n">
         <v>6</v>
@@ -2813,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -2845,46 +2912,46 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.623</v>
+        <v>0.615</v>
       </c>
       <c r="H14" t="n">
         <v>48.6</v>
       </c>
       <c r="I14" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J14" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
         <v>17.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.317</v>
+        <v>0.313</v>
       </c>
       <c r="O14" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P14" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R14" t="n">
         <v>11.7</v>
@@ -2893,13 +2960,13 @@
         <v>34</v>
       </c>
       <c r="T14" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="U14" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="V14" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W14" t="n">
         <v>6</v>
@@ -2914,16 +2981,16 @@
         <v>17.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>96.3</v>
+        <v>95.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2938,22 +3005,22 @@
         <v>6</v>
       </c>
       <c r="AI14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AM14" t="n">
         <v>18</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
@@ -2962,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2974,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV14" t="n">
         <v>19</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
         <v>9</v>
@@ -3126,7 +3193,7 @@
         <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
         <v>29</v>
@@ -3135,7 +3202,7 @@
         <v>29</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3147,7 +3214,7 @@
         <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
         <v>22</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -3209,64 +3276,64 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
         <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.725</v>
+        <v>0.74</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.479</v>
+        <v>0.482</v>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M16" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="N16" t="n">
-        <v>0.374</v>
+        <v>0.378</v>
       </c>
       <c r="O16" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="R16" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S16" t="n">
         <v>31.6</v>
       </c>
       <c r="T16" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U16" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V16" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X16" t="n">
         <v>5.4</v>
@@ -3275,16 +3342,16 @@
         <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.7</v>
+        <v>101.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="AD16" t="n">
         <v>25</v>
@@ -3299,13 +3366,13 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
         <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -3314,7 +3381,7 @@
         <v>20</v>
       </c>
       <c r="AM16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN16" t="n">
         <v>5</v>
@@ -3326,19 +3393,19 @@
         <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS16" t="n">
         <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
@@ -3347,16 +3414,16 @@
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -3469,22 +3536,22 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="n">
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
@@ -3508,31 +3575,31 @@
         <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
         <v>27</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
         <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX17" t="n">
         <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
-        <v>0.463</v>
+        <v>0.472</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3597,37 +3664,37 @@
         <v>0.435</v>
       </c>
       <c r="L18" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M18" t="n">
         <v>21.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O18" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="P18" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R18" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S18" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T18" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="U18" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W18" t="n">
         <v>7</v>
@@ -3642,34 +3709,34 @@
         <v>18.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF18" t="n">
         <v>19</v>
       </c>
-      <c r="AF18" t="n">
-        <v>21</v>
-      </c>
       <c r="AG18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI18" t="n">
         <v>19</v>
       </c>
       <c r="AJ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK18" t="n">
         <v>25</v>
@@ -3687,13 +3754,13 @@
         <v>4</v>
       </c>
       <c r="AP18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR18" t="n">
         <v>5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7</v>
       </c>
       <c r="AS18" t="n">
         <v>8</v>
@@ -3705,7 +3772,7 @@
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3912,7 @@
         <v>24</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
@@ -3857,7 +3924,7 @@
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>2</v>
@@ -3875,7 +3942,7 @@
         <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -3937,22 +4004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" t="n">
         <v>13</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>0.245</v>
+        <v>0.25</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J20" t="n">
         <v>78.40000000000001</v>
@@ -3964,22 +4031,22 @@
         <v>3.9</v>
       </c>
       <c r="M20" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P20" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S20" t="n">
         <v>29.9</v>
@@ -3991,31 +4058,31 @@
         <v>20.8</v>
       </c>
       <c r="V20" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>20.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>88.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4.8</v>
+        <v>-4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>28</v>
@@ -4054,13 +4121,13 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4069,16 +4136,16 @@
         <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>16</v>
@@ -4209,7 +4276,7 @@
         <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>10</v>
@@ -4227,7 +4294,7 @@
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
@@ -4239,7 +4306,7 @@
         <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
         <v>13</v>
@@ -4266,7 +4333,7 @@
         <v>24</v>
       </c>
       <c r="BA21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB21" t="n">
         <v>13</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.769</v>
+        <v>0.765</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,7 +4386,7 @@
         <v>37.7</v>
       </c>
       <c r="J22" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.478</v>
@@ -4328,34 +4395,34 @@
         <v>7.2</v>
       </c>
       <c r="M22" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O22" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
       <c r="R22" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U22" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="V22" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W22" t="n">
         <v>7.6</v>
@@ -4367,25 +4434,25 @@
         <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD22" t="n">
         <v>20</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
         <v>2</v>
@@ -4394,10 +4461,10 @@
         <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK22" t="n">
         <v>2</v>
@@ -4406,7 +4473,7 @@
         <v>8</v>
       </c>
       <c r="AM22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN22" t="n">
         <v>10</v>
@@ -4427,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>28</v>
@@ -4442,16 +4509,16 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -4483,97 +4550,97 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" t="n">
         <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>0.604</v>
+        <v>0.615</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J23" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L23" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="O23" t="n">
         <v>15.3</v>
       </c>
       <c r="P23" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.645</v>
+        <v>0.643</v>
       </c>
       <c r="R23" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T23" t="n">
         <v>42.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W23" t="n">
         <v>6.7</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
         <v>4.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AA23" t="n">
         <v>20.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.3</v>
+        <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE23" t="n">
         <v>5</v>
       </c>
-      <c r="AE23" t="n">
-        <v>6</v>
-      </c>
       <c r="AF23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -4594,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
         <v>9</v>
@@ -4636,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>5.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF24" t="n">
         <v>11</v>
@@ -4758,7 +4825,7 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
         <v>4</v>
@@ -4791,10 +4858,10 @@
         <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
@@ -4803,7 +4870,7 @@
         <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -4847,52 +4914,52 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
         <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J25" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L25" t="n">
         <v>6.5</v>
       </c>
       <c r="M25" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O25" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P25" t="n">
         <v>21</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="R25" t="n">
         <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T25" t="n">
         <v>41.5</v>
@@ -4901,13 +4968,13 @@
         <v>22.6</v>
       </c>
       <c r="V25" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W25" t="n">
         <v>6.8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
@@ -4922,10 +4989,10 @@
         <v>96.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>18</v>
@@ -4943,52 +5010,52 @@
         <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT25" t="n">
         <v>21</v>
       </c>
       <c r="AU25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -5029,34 +5096,34 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.472</v>
+        <v>0.462</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J26" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L26" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M26" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="N26" t="n">
         <v>0.341</v>
@@ -5068,25 +5135,25 @@
         <v>21.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="R26" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S26" t="n">
         <v>29.7</v>
       </c>
       <c r="T26" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U26" t="n">
         <v>20.6</v>
       </c>
       <c r="V26" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X26" t="n">
         <v>5.1</v>
@@ -5098,28 +5165,28 @@
         <v>19.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.2</v>
+        <v>96.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
         <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
@@ -5128,7 +5195,7 @@
         <v>12</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL26" t="n">
         <v>11</v>
@@ -5137,22 +5204,22 @@
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO26" t="n">
         <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5161,10 +5228,10 @@
         <v>18</v>
       </c>
       <c r="AV26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
         <v>15</v>
@@ -5179,7 +5246,7 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
         <v>16</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,10 +5368,10 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
@@ -5313,13 +5380,13 @@
         <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO27" t="n">
         <v>10</v>
@@ -5337,7 +5404,7 @@
         <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
@@ -5358,7 +5425,7 @@
         <v>14</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
         <v>8</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>4.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG28" t="n">
         <v>4</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK28" t="n">
         <v>4</v>
@@ -5504,13 +5571,13 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
@@ -5522,13 +5589,13 @@
         <v>13</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX28" t="n">
         <v>25</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
         <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J29" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L29" t="n">
         <v>5.5</v>
@@ -5605,16 +5672,16 @@
         <v>16.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.334</v>
+        <v>0.336</v>
       </c>
       <c r="O29" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P29" t="n">
         <v>21.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
@@ -5623,13 +5690,13 @@
         <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U29" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V29" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W29" t="n">
         <v>6.8</v>
@@ -5641,22 +5708,22 @@
         <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.8</v>
+        <v>91.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF29" t="n">
         <v>26</v>
@@ -5665,7 +5732,7 @@
         <v>27</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
@@ -5677,7 +5744,7 @@
         <v>19</v>
       </c>
       <c r="AL29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="n">
         <v>20</v>
@@ -5692,13 +5759,13 @@
         <v>16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
         <v>23</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>22</v>
@@ -5707,7 +5774,7 @@
         <v>12</v>
       </c>
       <c r="AV29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5880,7 +5947,7 @@
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT30" t="n">
         <v>4</v>
@@ -5892,19 +5959,19 @@
         <v>10</v>
       </c>
       <c r="AW30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX30" t="n">
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" t="n">
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G31" t="n">
-        <v>0.231</v>
+        <v>0.235</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5957,19 +6024,19 @@
         <v>36.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M31" t="n">
         <v>16.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.319</v>
+        <v>0.317</v>
       </c>
       <c r="O31" t="n">
         <v>15.5</v>
@@ -5978,25 +6045,25 @@
         <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T31" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="U31" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="V31" t="n">
         <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X31" t="n">
         <v>6.6</v>
@@ -6008,7 +6075,7 @@
         <v>21.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB31" t="n">
         <v>93.09999999999999</v>
@@ -6017,7 +6084,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6032,10 +6099,10 @@
         <v>26</v>
       </c>
       <c r="AI31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK31" t="n">
         <v>24</v>
@@ -6050,7 +6117,7 @@
         <v>24</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
@@ -6062,10 +6129,10 @@
         <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
@@ -6080,7 +6147,7 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-1-2011-12</t>
+          <t>2012-04-01</t>
         </is>
       </c>
     </row>
